--- a/docs/工作/04-营销推广/Sakuranomori种草/笔记种草预算分配表.xlsx
+++ b/docs/工作/04-营销推广/Sakuranomori种草/笔记种草预算分配表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="小紅書ノート予算配分" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ノート予算配分" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,9 +18,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="¥#,##0"/>
-    <numFmt numFmtId="165" formatCode="¥#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,20 +37,61 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="14"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00BF6000"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00BF6000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -69,19 +110,8 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00375623"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -90,12 +120,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9C47F"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,6 +136,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9C47F"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,58 +180,89 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -557,696 +628,1384 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>小紅書 ノート(種草)予算配分 ／ 小红书笔记种草预算分配 —— Sakuranomori · Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ノート総予算
-笔记总预算(円)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>総投稿数
-总篇数</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>想定総インプレ
-预期总曝光</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>平均CPM(円)
-千次曝光成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="C3" s="4">
-        <f>D26</f>
-        <v/>
-      </c>
-      <c r="E3" s="4">
-        <f>G26</f>
-        <v/>
-      </c>
-      <c r="G3" s="5">
-        <f>IF(G26=0,"",F26/G26*1000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+          <t>小紅書 ノート(種草)予算配分 ／ 小红书笔记种草预算分配 —— Sakuranomori</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>① 年度総括 ／ 年度总览（简单汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>年度ノート予算
+全年预算(手填)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>本四半期予算
+本季度(自动)</t>
+        </is>
+      </c>
+      <c r="D4" s="5">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>本四半期占比</t>
+        </is>
+      </c>
+      <c r="F4" s="6">
+        <f>IF($B$4=0,"",$D$4/$B$4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>年度想定インプレ
+全年曝光(手填)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>※本季度=下方3个月自动合计；全年为手填目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>② 四半期（3ヶ月）総括 ／ 季度汇总（自动·简单）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>指標 / 指标</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>予算(円) 预算</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>F30</f>
+        <v/>
+      </c>
+      <c r="C8" s="12">
+        <f>F45</f>
+        <v/>
+      </c>
+      <c r="D8" s="12">
+        <f>F60</f>
+        <v/>
+      </c>
+      <c r="E8" s="13">
+        <f>SUM(B8:D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>投稿数 篇数</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
+        <f>D30</f>
+        <v/>
+      </c>
+      <c r="C9" s="14">
+        <f>D45</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
+        <f>D60</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>SUM(B9:D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>想定インプレ 曝光</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="C10" s="14">
+        <f>G45</f>
+        <v/>
+      </c>
+      <c r="D10" s="14">
+        <f>G60</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>SUM(B10:D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>想定エンゲージ 互动</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>H30</f>
+        <v/>
+      </c>
+      <c r="C11" s="14">
+        <f>H45</f>
+        <v/>
+      </c>
+      <c r="D11" s="14">
+        <f>H60</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
+        <f>SUM(B11:D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>CPM(円) 千次曝光成本</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <f>IF(B10=0,"",B8/B10*1000)</f>
+        <v/>
+      </c>
+      <c r="C12" s="14">
+        <f>IF(C10=0,"",C8/C10*1000)</f>
+        <v/>
+      </c>
+      <c r="D12" s="14">
+        <f>IF(D10=0,"",D8/D10*1000)</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>IF(E10=0,"",E8/E10*1000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>③ 月別明細 ／ 月度明细（主要·按达人细分，黄色手填/灰色自动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>■ 8月 明細</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>アカウント名
 账号</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>フォロワー層
-粉丝层级</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+层级</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>投稿形式
 形式</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>投稿数
 篇数</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>単価(円)
-单篇稿费</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+单价</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>支払金額(円)
 小计</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>想定インプレ
 预期曝光</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>想定エンゲージ
 预期互动</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>CPM(円)
-千次曝光成本</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>CPM(円)</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>備考
 备注</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>欧淋莉</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>腰部</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>動画(视频)</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E18" s="20" t="n">
         <v>45000</v>
       </c>
-      <c r="F6" s="10">
-        <f>IF(OR(D6="",E6=""),"",D6*E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="F18" s="21">
+        <f>IF(OR(D18="",E18=""),"",D18*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="22" t="n">
         <v>120000</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H18" s="22" t="n">
         <v>3600</v>
       </c>
-      <c r="I6" s="12">
-        <f>IF(OR(F6="",G6="",G6=0),"",F6/G6*1000)</f>
-        <v/>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>直播档同期配合1条种草</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="I18" s="23">
+        <f>IF(OR(F18="",G18="",G18=0),"",F18/G18*1000)</f>
+        <v/>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>直播同期配合</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>如酱在东京</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>腰部</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D19" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E19" s="20" t="n">
         <v>40000</v>
       </c>
-      <c r="F7" s="10">
-        <f>IF(OR(D7="",E7=""),"",D7*E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="11" t="n">
+      <c r="F19" s="21">
+        <f>IF(OR(D19="",E19=""),"",D19*E19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="22" t="n">
         <v>80000</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H19" s="22" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" s="12">
-        <f>IF(OR(F7="",G7="",G7=0),"",F7/G7*1000)</f>
-        <v/>
-      </c>
-      <c r="J7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>单眼皮的妮可</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="I19" s="23">
+        <f>IF(OR(F19="",G19="",G19=0),"",F19/G19*1000)</f>
+        <v/>
+      </c>
+      <c r="J19" s="18" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>KOC铺量·多人</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>KOC</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="9" t="n">
+      <c r="D20" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="20" t="n">
         <v>5000</v>
       </c>
-      <c r="F8" s="10">
-        <f>IF(OR(D8="",E8=""),"",D8*E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>600</v>
-      </c>
-      <c r="I8" s="12">
-        <f>IF(OR(F8="",G8="",G8=0),"",F8/G8*1000)</f>
-        <v/>
-      </c>
-      <c r="J8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>(头部造势·待定)</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>頭部</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>動画(视频)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F9" s="10">
-        <f>IF(OR(D9="",E9=""),"",D9*E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>300000</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I9" s="12">
-        <f>IF(OR(F9="",G9="",G9=0),"",F9/G9*1000)</f>
-        <v/>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>10月双11前造势</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>KOC铺量·多人</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>KOC</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>画像(图文)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F10" s="10">
-        <f>IF(OR(D10="",E10=""),"",D10*E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="11" t="n">
+      <c r="F20" s="21">
+        <f>IF(OR(D20="",E20=""),"",D20*E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H20" s="22" t="n">
         <v>480</v>
       </c>
-      <c r="I10" s="12">
-        <f>IF(OR(F10="",G10="",G10=0),"",F10/G10*1000)</f>
-        <v/>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="I20" s="23">
+        <f>IF(OR(F20="",G20="",G20=0),"",F20/G20*1000)</f>
+        <v/>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>真实体验铺搜索</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="10">
-        <f>IF(OR(D11="",E11=""),"",D11*E11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="12">
-        <f>IF(OR(F11="",G11="",G11=0),"",F11/G11*1000)</f>
-        <v/>
-      </c>
-      <c r="J11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="10">
-        <f>IF(OR(D12="",E12=""),"",D12*E12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="12">
-        <f>IF(OR(F12="",G12="",G12=0),"",F12/G12*1000)</f>
-        <v/>
-      </c>
-      <c r="J12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="10">
-        <f>IF(OR(D13="",E13=""),"",D13*E13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="12">
-        <f>IF(OR(F13="",G13="",G13=0),"",F13/G13*1000)</f>
-        <v/>
-      </c>
-      <c r="J13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="10">
-        <f>IF(OR(D14="",E14=""),"",D14*E14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="12">
-        <f>IF(OR(F14="",G14="",G14=0),"",F14/G14*1000)</f>
-        <v/>
-      </c>
-      <c r="J14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="10">
-        <f>IF(OR(D15="",E15=""),"",D15*E15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="12">
-        <f>IF(OR(F15="",G15="",G15=0),"",F15/G15*1000)</f>
-        <v/>
-      </c>
-      <c r="J15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10">
-        <f>IF(OR(D16="",E16=""),"",D16*E16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="12">
-        <f>IF(OR(F16="",G16="",G16=0),"",F16/G16*1000)</f>
-        <v/>
-      </c>
-      <c r="J16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10">
-        <f>IF(OR(D17="",E17=""),"",D17*E17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="12">
-        <f>IF(OR(F17="",G17="",G17=0),"",F17/G17*1000)</f>
-        <v/>
-      </c>
-      <c r="J17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10">
-        <f>IF(OR(D18="",E18=""),"",D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="12">
-        <f>IF(OR(F18="",G18="",G18=0),"",F18/G18*1000)</f>
-        <v/>
-      </c>
-      <c r="J18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10">
-        <f>IF(OR(D19="",E19=""),"",D19*E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="12">
-        <f>IF(OR(F19="",G19="",G19=0),"",F19/G19*1000)</f>
-        <v/>
-      </c>
-      <c r="J19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10">
-        <f>IF(OR(D20="",E20=""),"",D20*E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="12">
-        <f>IF(OR(F20="",G20="",G20=0),"",F20/G20*1000)</f>
-        <v/>
-      </c>
-      <c r="J20" s="7" t="n"/>
-    </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="21">
         <f>IF(OR(D21="",E21=""),"",D21*E21)</f>
         <v/>
       </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="12">
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="23">
         <f>IF(OR(F21="",G21="",G21=0),"",F21/G21*1000)</f>
         <v/>
       </c>
-      <c r="J21" s="7" t="n"/>
+      <c r="J21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="21">
         <f>IF(OR(D22="",E22=""),"",D22*E22)</f>
         <v/>
       </c>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="12">
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="23">
         <f>IF(OR(F22="",G22="",G22=0),"",F22/G22*1000)</f>
         <v/>
       </c>
-      <c r="J22" s="7" t="n"/>
+      <c r="J22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="21">
         <f>IF(OR(D23="",E23=""),"",D23*E23)</f>
         <v/>
       </c>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="12">
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="23">
         <f>IF(OR(F23="",G23="",G23=0),"",F23/G23*1000)</f>
         <v/>
       </c>
-      <c r="J23" s="7" t="n"/>
+      <c r="J23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="21">
         <f>IF(OR(D24="",E24=""),"",D24*E24)</f>
         <v/>
       </c>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="12">
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="23">
         <f>IF(OR(F24="",G24="",G24=0),"",F24/G24*1000)</f>
         <v/>
       </c>
-      <c r="J24" s="7" t="n"/>
+      <c r="J24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="21">
         <f>IF(OR(D25="",E25=""),"",D25*E25)</f>
         <v/>
       </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="12">
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="23">
         <f>IF(OR(F25="",G25="",G25=0),"",F25/G25*1000)</f>
         <v/>
       </c>
-      <c r="J25" s="7" t="n"/>
+      <c r="J25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>合計 ／ 合计</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14">
-        <f>SUM(D6:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="15">
-        <f>SUM(F6:F25)</f>
-        <v/>
-      </c>
-      <c r="G26" s="16">
-        <f>SUM(G6:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="16">
-        <f>SUM(H6:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="16">
-        <f>IF(G26=0,"",F26/G26*1000)</f>
-        <v/>
-      </c>
-      <c r="J26" s="14" t="n"/>
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="21">
+        <f>IF(OR(D26="",E26=""),"",D26*E26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="23">
+        <f>IF(OR(F26="",G26="",G26=0),"",F26/G26*1000)</f>
+        <v/>
+      </c>
+      <c r="J26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="21">
+        <f>IF(OR(D27="",E27=""),"",D27*E27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="23">
+        <f>IF(OR(F27="",G27="",G27=0),"",F27/G27*1000)</f>
+        <v/>
+      </c>
+      <c r="J27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>填写说明 / 記入方法</t>
-        </is>
-      </c>
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="21">
+        <f>IF(OR(D28="",E28=""),"",D28*E28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="23">
+        <f>IF(OR(F28="",G28="",G28=0),"",F28/G28*1000)</f>
+        <v/>
+      </c>
+      <c r="J28" s="18" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>· 黄色格=手填(账号/层级/形式/篇数/単価/预期曝光/预期互动)；灰色格=自动(小计/CPM)。</t>
-        </is>
-      </c>
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="21">
+        <f>IF(OR(D29="",E29=""),"",D29*E29)</f>
+        <v/>
+      </c>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="23">
+        <f>IF(OR(F29="",G29="",G29=0),"",F29/G29*1000)</f>
+        <v/>
+      </c>
+      <c r="J29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>· 支払金額(小计)=単価×投稿数；CPM=支払金額÷曝光×1000(千次曝光成本，越低越划算)。</t>
-        </is>
-      </c>
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>8月 月計 / 月合计</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="26">
+        <f>SUM(D18:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="27">
+        <f>SUM(F18:F29)</f>
+        <v/>
+      </c>
+      <c r="G30" s="26">
+        <f>SUM(G18:G29)</f>
+        <v/>
+      </c>
+      <c r="H30" s="26">
+        <f>SUM(H18:H29)</f>
+        <v/>
+      </c>
+      <c r="I30" s="26">
+        <f>IF(G30=0,"",F30/G30*1000)</f>
+        <v/>
+      </c>
+      <c r="J30" s="25" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>· 顶部四个大数(总预算/总篇数/预期总曝光/平均CPM)随下方明细自动更新。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>· 想定インプレ/エンゲージ=预估曝光/互动，签约前按达人历史均值填；投后可回填实际值对比。</t>
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>■ 9月 明細</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>アカウント名
+账号</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>フォロワー層
+层级</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>投稿形式
+形式</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>投稿数
+篇数</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>単価(円)
+单价</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>支払金額(円)
+小计</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>想定インプレ
+预期曝光</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>想定エンゲージ
+预期互动</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>CPM(円)</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>備考
+备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>· 数字均为日元(¥)。示例行请替换为真实数据。</t>
-        </is>
-      </c>
+          <t>单眼皮的妮可</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>KOC</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>画像(图文)</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F33" s="21">
+        <f>IF(OR(D33="",E33=""),"",D33*E33)</f>
+        <v/>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>600</v>
+      </c>
+      <c r="I33" s="23">
+        <f>IF(OR(F33="",G33="",G33=0),"",F33/G33*1000)</f>
+        <v/>
+      </c>
+      <c r="J33" s="18" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>(头部造势·待定)</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>頭部</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>動画(视频)</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F34" s="21">
+        <f>IF(OR(D34="",E34=""),"",D34*E34)</f>
+        <v/>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I34" s="23">
+        <f>IF(OR(F34="",G34="",G34=0),"",F34/G34*1000)</f>
+        <v/>
+      </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>造势</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>腰部攻略</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>腰部</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>画像(图文)</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F35" s="21">
+        <f>IF(OR(D35="",E35=""),"",D35*E35)</f>
+        <v/>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H35" s="22" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I35" s="23">
+        <f>IF(OR(F35="",G35="",G35=0),"",F35/G35*1000)</f>
+        <v/>
+      </c>
+      <c r="J35" s="18" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="21">
+        <f>IF(OR(D36="",E36=""),"",D36*E36)</f>
+        <v/>
+      </c>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="23">
+        <f>IF(OR(F36="",G36="",G36=0),"",F36/G36*1000)</f>
+        <v/>
+      </c>
+      <c r="J36" s="18" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="n"/>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="21">
+        <f>IF(OR(D37="",E37=""),"",D37*E37)</f>
+        <v/>
+      </c>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="23">
+        <f>IF(OR(F37="",G37="",G37=0),"",F37/G37*1000)</f>
+        <v/>
+      </c>
+      <c r="J37" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="21">
+        <f>IF(OR(D38="",E38=""),"",D38*E38)</f>
+        <v/>
+      </c>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="23">
+        <f>IF(OR(F38="",G38="",G38=0),"",F38/G38*1000)</f>
+        <v/>
+      </c>
+      <c r="J38" s="18" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="21">
+        <f>IF(OR(D39="",E39=""),"",D39*E39)</f>
+        <v/>
+      </c>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="23">
+        <f>IF(OR(F39="",G39="",G39=0),"",F39/G39*1000)</f>
+        <v/>
+      </c>
+      <c r="J39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n"/>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="21">
+        <f>IF(OR(D40="",E40=""),"",D40*E40)</f>
+        <v/>
+      </c>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="23">
+        <f>IF(OR(F40="",G40="",G40=0),"",F40/G40*1000)</f>
+        <v/>
+      </c>
+      <c r="J40" s="18" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="n"/>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="19" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="21">
+        <f>IF(OR(D41="",E41=""),"",D41*E41)</f>
+        <v/>
+      </c>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="23">
+        <f>IF(OR(F41="",G41="",G41=0),"",F41/G41*1000)</f>
+        <v/>
+      </c>
+      <c r="J41" s="18" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="n"/>
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="21">
+        <f>IF(OR(D42="",E42=""),"",D42*E42)</f>
+        <v/>
+      </c>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="23">
+        <f>IF(OR(F42="",G42="",G42=0),"",F42/G42*1000)</f>
+        <v/>
+      </c>
+      <c r="J42" s="18" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="n"/>
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="21">
+        <f>IF(OR(D43="",E43=""),"",D43*E43)</f>
+        <v/>
+      </c>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="23">
+        <f>IF(OR(F43="",G43="",G43=0),"",F43/G43*1000)</f>
+        <v/>
+      </c>
+      <c r="J43" s="18" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="n"/>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="21">
+        <f>IF(OR(D44="",E44=""),"",D44*E44)</f>
+        <v/>
+      </c>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="23">
+        <f>IF(OR(F44="",G44="",G44=0),"",F44/G44*1000)</f>
+        <v/>
+      </c>
+      <c r="J44" s="18" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>9月 月計 / 月合计</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="25" t="n"/>
+      <c r="D45" s="26">
+        <f>SUM(D33:D44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="27">
+        <f>SUM(F33:F44)</f>
+        <v/>
+      </c>
+      <c r="G45" s="26">
+        <f>SUM(G33:G44)</f>
+        <v/>
+      </c>
+      <c r="H45" s="26">
+        <f>SUM(H33:H44)</f>
+        <v/>
+      </c>
+      <c r="I45" s="26">
+        <f>IF(G45=0,"",F45/G45*1000)</f>
+        <v/>
+      </c>
+      <c r="J45" s="25" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>■ 10月 明細</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>アカウント名
+账号</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>フォロワー層
+层级</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>投稿形式
+形式</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>投稿数
+篇数</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>単価(円)
+单价</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>支払金額(円)
+小计</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>想定インプレ
+预期曝光</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>想定エンゲージ
+预期互动</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>CPM(円)</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>備考
+备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>KOC铺量·多人</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>KOC</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>画像(图文)</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F48" s="21">
+        <f>IF(OR(D48="",E48=""),"",D48*E48)</f>
+        <v/>
+      </c>
+      <c r="G48" s="22" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>480</v>
+      </c>
+      <c r="I48" s="23">
+        <f>IF(OR(F48="",G48="",G48=0),"",F48/G48*1000)</f>
+        <v/>
+      </c>
+      <c r="J48" s="18" t="inlineStr">
+        <is>
+          <t>双11蓄水</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>腰部攻略</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>腰部</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>画像(图文)</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F49" s="21">
+        <f>IF(OR(D49="",E49=""),"",D49*E49)</f>
+        <v/>
+      </c>
+      <c r="G49" s="22" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H49" s="22" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I49" s="23">
+        <f>IF(OR(F49="",G49="",G49=0),"",F49/G49*1000)</f>
+        <v/>
+      </c>
+      <c r="J49" s="18" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="n"/>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
+      <c r="E50" s="20" t="n"/>
+      <c r="F50" s="21">
+        <f>IF(OR(D50="",E50=""),"",D50*E50)</f>
+        <v/>
+      </c>
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="23">
+        <f>IF(OR(F50="",G50="",G50=0),"",F50/G50*1000)</f>
+        <v/>
+      </c>
+      <c r="J50" s="18" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n"/>
+      <c r="B51" s="19" t="n"/>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="21">
+        <f>IF(OR(D51="",E51=""),"",D51*E51)</f>
+        <v/>
+      </c>
+      <c r="G51" s="22" t="n"/>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="23">
+        <f>IF(OR(F51="",G51="",G51=0),"",F51/G51*1000)</f>
+        <v/>
+      </c>
+      <c r="J51" s="18" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="n"/>
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="21">
+        <f>IF(OR(D52="",E52=""),"",D52*E52)</f>
+        <v/>
+      </c>
+      <c r="G52" s="22" t="n"/>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="23">
+        <f>IF(OR(F52="",G52="",G52=0),"",F52/G52*1000)</f>
+        <v/>
+      </c>
+      <c r="J52" s="18" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="n"/>
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="21">
+        <f>IF(OR(D53="",E53=""),"",D53*E53)</f>
+        <v/>
+      </c>
+      <c r="G53" s="22" t="n"/>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="23">
+        <f>IF(OR(F53="",G53="",G53=0),"",F53/G53*1000)</f>
+        <v/>
+      </c>
+      <c r="J53" s="18" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="n"/>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="20" t="n"/>
+      <c r="F54" s="21">
+        <f>IF(OR(D54="",E54=""),"",D54*E54)</f>
+        <v/>
+      </c>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="23">
+        <f>IF(OR(F54="",G54="",G54=0),"",F54/G54*1000)</f>
+        <v/>
+      </c>
+      <c r="J54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="n"/>
+      <c r="B55" s="19" t="n"/>
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="21">
+        <f>IF(OR(D55="",E55=""),"",D55*E55)</f>
+        <v/>
+      </c>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="22" t="n"/>
+      <c r="I55" s="23">
+        <f>IF(OR(F55="",G55="",G55=0),"",F55/G55*1000)</f>
+        <v/>
+      </c>
+      <c r="J55" s="18" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="n"/>
+      <c r="B56" s="19" t="n"/>
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="21">
+        <f>IF(OR(D56="",E56=""),"",D56*E56)</f>
+        <v/>
+      </c>
+      <c r="G56" s="22" t="n"/>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="23">
+        <f>IF(OR(F56="",G56="",G56=0),"",F56/G56*1000)</f>
+        <v/>
+      </c>
+      <c r="J56" s="18" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="n"/>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="19" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="21">
+        <f>IF(OR(D57="",E57=""),"",D57*E57)</f>
+        <v/>
+      </c>
+      <c r="G57" s="22" t="n"/>
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="23">
+        <f>IF(OR(F57="",G57="",G57=0),"",F57/G57*1000)</f>
+        <v/>
+      </c>
+      <c r="J57" s="18" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="n"/>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="20" t="n"/>
+      <c r="F58" s="21">
+        <f>IF(OR(D58="",E58=""),"",D58*E58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="22" t="n"/>
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="23">
+        <f>IF(OR(F58="",G58="",G58=0),"",F58/G58*1000)</f>
+        <v/>
+      </c>
+      <c r="J58" s="18" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="n"/>
+      <c r="B59" s="19" t="n"/>
+      <c r="C59" s="19" t="n"/>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="20" t="n"/>
+      <c r="F59" s="21">
+        <f>IF(OR(D59="",E59=""),"",D59*E59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="22" t="n"/>
+      <c r="H59" s="22" t="n"/>
+      <c r="I59" s="23">
+        <f>IF(OR(F59="",G59="",G59=0),"",F59/G59*1000)</f>
+        <v/>
+      </c>
+      <c r="J59" s="18" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>10月 月計 / 月合计</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="n"/>
+      <c r="C60" s="25" t="n"/>
+      <c r="D60" s="26">
+        <f>SUM(D48:D59)</f>
+        <v/>
+      </c>
+      <c r="E60" s="25" t="n"/>
+      <c r="F60" s="27">
+        <f>SUM(F48:F59)</f>
+        <v/>
+      </c>
+      <c r="G60" s="26">
+        <f>SUM(G48:G59)</f>
+        <v/>
+      </c>
+      <c r="H60" s="26">
+        <f>SUM(H48:H59)</f>
+        <v/>
+      </c>
+      <c r="I60" s="26">
+        <f>IF(G60=0,"",F60/G60*1000)</f>
+        <v/>
+      </c>
+      <c r="J60" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A16:J16"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="B6:B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="6">
+    <dataValidation sqref="B18:B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"頭部,腰部,尾部,KOC"</formula1>
     </dataValidation>
-    <dataValidation sqref="C6:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C18:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"画像(图文),動画(视频)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33:B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"頭部,腰部,尾部,KOC"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C33:C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"画像(图文),動画(视频)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48:B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"頭部,腰部,尾部,KOC"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C48:C59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"画像(图文),動画(视频)"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/工作/04-营销推广/Sakuranomori种草/笔记种草预算分配表.xlsx
+++ b/docs/工作/04-营销推广/Sakuranomori种草/笔记种草预算分配表.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="¥#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,7 +44,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -55,7 +55,7 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00808080"/>
-      <sz val="8"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -73,13 +73,13 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00375623"/>
-      <sz val="12"/>
+      <color rgb="00BF6000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -110,8 +110,19 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -153,6 +164,11 @@
         <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -180,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -227,6 +243,15 @@
     <xf numFmtId="3" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -242,9 +267,6 @@
     <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -262,6 +284,12 @@
     </xf>
     <xf numFmtId="164" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -628,25 +656,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>小紅書 ノート(種草)予算配分 ／ 小红书笔记种草预算分配 —— Sakuranomori</t>
+          <t>小紅書 ノート(種草)予算配分・効果 ／ 小红书笔记种草预算与效果 —— Sakuranomori</t>
         </is>
       </c>
     </row>
@@ -657,10 +686,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>年度ノート予算
+          <t>年度予算
 全年预算(手填)</t>
         </is>
       </c>
@@ -688,23 +717,33 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>年度想定インプレ
-全年曝光(手填)</t>
+          <t>年度想定曝光
+全年(手填)</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
         <v>5000000</v>
       </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>※本季度=下方3个月自动合计；全年为手填目标</t>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>年度想定互动
+全年(手填)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>※本季度=下方3个月自动合计
+全年为手填目标</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>② 四半期（3ヶ月）総括 ／ 季度汇总（自动·简单）</t>
+          <t>② 四半期（3ヶ月）総括 ／ 季度汇总（自动·给品牌方看）</t>
         </is>
       </c>
     </row>
@@ -742,15 +781,15 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>F30</f>
+        <f>E33</f>
         <v/>
       </c>
       <c r="C8" s="12">
-        <f>F45</f>
+        <f>E48</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>F60</f>
+        <f>E63</f>
         <v/>
       </c>
       <c r="E8" s="13">
@@ -765,15 +804,15 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>D30</f>
+        <f>D33</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>D45</f>
+        <f>D48</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>D60</f>
+        <f>D63</f>
         <v/>
       </c>
       <c r="E9" s="15">
@@ -788,15 +827,15 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>G30</f>
+        <f>F33</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>G45</f>
+        <f>F48</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>G60</f>
+        <f>F63</f>
         <v/>
       </c>
       <c r="E10" s="15">
@@ -811,15 +850,15 @@
         </is>
       </c>
       <c r="B11" s="14">
-        <f>H30</f>
+        <f>G33</f>
         <v/>
       </c>
       <c r="C11" s="14">
-        <f>H45</f>
+        <f>G48</f>
         <v/>
       </c>
       <c r="D11" s="14">
-        <f>H60</f>
+        <f>G63</f>
         <v/>
       </c>
       <c r="E11" s="15">
@@ -830,1182 +869,1403 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>CPM(円) 千次曝光成本</t>
-        </is>
-      </c>
-      <c r="B12" s="14">
+          <t>エンゲージ率 互动率</t>
+        </is>
+      </c>
+      <c r="B12" s="16">
+        <f>IF(B10=0,"",B11/B10)</f>
+        <v/>
+      </c>
+      <c r="C12" s="16">
+        <f>IF(C10=0,"",C11/C10)</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>IF(D10=0,"",D11/D10)</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>IF(E10=0,"",E11/E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>想定保存 收藏</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>H33</f>
+        <v/>
+      </c>
+      <c r="C13" s="14">
+        <f>H48</f>
+        <v/>
+      </c>
+      <c r="D13" s="14">
+        <f>H63</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>SUM(B13:D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>CPM(円)</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
         <f>IF(B10=0,"",B8/B10*1000)</f>
         <v/>
       </c>
-      <c r="C12" s="14">
+      <c r="C14" s="14">
         <f>IF(C10=0,"",C8/C10*1000)</f>
         <v/>
       </c>
-      <c r="D12" s="14">
+      <c r="D14" s="14">
         <f>IF(D10=0,"",D8/D10*1000)</f>
         <v/>
       </c>
-      <c r="E12" s="15">
+      <c r="E14" s="15">
         <f>IF(E10=0,"",E8/E10*1000)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>③ 月別明細 ／ 月度明细（主要·按达人细分，黄色手填/灰色自动）</t>
-        </is>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>CPE(円) 单次互动成本</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>IF(B11=0,"",B8/B11)</f>
+        <v/>
+      </c>
+      <c r="C15" s="14">
+        <f>IF(C11=0,"",C8/C11)</f>
+        <v/>
+      </c>
+      <c r="D15" s="14">
+        <f>IF(D11=0,"",D8/D11)</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>IF(E11=0,"",E8/E11)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>③ 种草衔接（投后回填 · 品牌方最关心）→ 见下方说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>④ 月別明細 ／ 月度明细（主要·按达人细分；黄=手填，灰=自动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>■ 8月 明細</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>アカウント名
 账号</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>フォロワー層
-层级</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>層級</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>投稿形式
 形式</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>投稿数
 篇数</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>単価(円)
-单价</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>支払金額(円)
-小计</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>稿費(円)
+稿费</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>想定インプレ
-预期曝光</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
+预估曝光</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>想定エンゲージ
-预期互动</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
+预估互动</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>想定保存
+预估收藏</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>CPM(円)</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>備考
-备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>CPE(円)
+单次互动</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>欧淋莉</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>腰部</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>動画(视频)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E21" s="23" t="n">
         <v>45000</v>
       </c>
-      <c r="F18" s="21">
-        <f>IF(OR(D18="",E18=""),"",D18*E18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="22" t="n">
+      <c r="F21" s="24" t="n">
         <v>120000</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="G21" s="24" t="n">
         <v>3600</v>
       </c>
-      <c r="I18" s="23">
-        <f>IF(OR(F18="",G18="",G18=0),"",F18/G18*1000)</f>
-        <v/>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="H21" s="24" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I21" s="25">
+        <f>IF(OR(E21="",F21="",F21=0),"",E21/F21*1000)</f>
+        <v/>
+      </c>
+      <c r="J21" s="25">
+        <f>IF(OR(E21="",G21="",G21=0),"",E21/G21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>直播同期配合</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>如酱在东京</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>腰部</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D22" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E22" s="23" t="n">
         <v>40000</v>
       </c>
-      <c r="F19" s="21">
-        <f>IF(OR(D19="",E19=""),"",D19*E19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="22" t="n">
+      <c r="F22" s="24" t="n">
         <v>80000</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="G22" s="24" t="n">
         <v>2400</v>
       </c>
-      <c r="I19" s="23">
-        <f>IF(OR(F19="",G19="",G19=0),"",F19/G19*1000)</f>
-        <v/>
-      </c>
-      <c r="J19" s="18" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="H22" s="24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="25">
+        <f>IF(OR(E22="",F22="",F22=0),"",E22/F22*1000)</f>
+        <v/>
+      </c>
+      <c r="J22" s="25">
+        <f>IF(OR(E22="",G22="",G22=0),"",E22/G22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>KOC铺量·多人</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>KOC</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D23" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E23" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="F20" s="21">
-        <f>IF(OR(D20="",E20=""),"",D20*E20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="22" t="n">
+      <c r="F23" s="24" t="n">
         <v>12000</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="G23" s="24" t="n">
         <v>480</v>
       </c>
-      <c r="I20" s="23">
-        <f>IF(OR(F20="",G20="",G20=0),"",F20/G20*1000)</f>
-        <v/>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
+      <c r="H23" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="I23" s="25">
+        <f>IF(OR(E23="",F23="",F23=0),"",E23/F23*1000)</f>
+        <v/>
+      </c>
+      <c r="J23" s="25">
+        <f>IF(OR(E23="",G23="",G23=0),"",E23/G23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>真实体验铺搜索</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="18" t="n"/>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="21">
-        <f>IF(OR(D21="",E21=""),"",D21*E21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="23">
-        <f>IF(OR(F21="",G21="",G21=0),"",F21/G21*1000)</f>
-        <v/>
-      </c>
-      <c r="J21" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n"/>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="21">
-        <f>IF(OR(D22="",E22=""),"",D22*E22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="23">
-        <f>IF(OR(F22="",G22="",G22=0),"",F22/G22*1000)</f>
-        <v/>
-      </c>
-      <c r="J22" s="18" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="n"/>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="21">
-        <f>IF(OR(D23="",E23=""),"",D23*E23)</f>
-        <v/>
-      </c>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="23">
-        <f>IF(OR(F23="",G23="",G23=0),"",F23/G23*1000)</f>
-        <v/>
-      </c>
-      <c r="J23" s="18" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="18" t="n"/>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="21">
-        <f>IF(OR(D24="",E24=""),"",D24*E24)</f>
-        <v/>
-      </c>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="23">
-        <f>IF(OR(F24="",G24="",G24=0),"",F24/G24*1000)</f>
-        <v/>
-      </c>
-      <c r="J24" s="18" t="n"/>
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="25">
+        <f>IF(OR(E24="",F24="",F24=0),"",E24/F24*1000)</f>
+        <v/>
+      </c>
+      <c r="J24" s="25">
+        <f>IF(OR(E24="",G24="",G24=0),"",E24/G24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="21" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n"/>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="21">
-        <f>IF(OR(D25="",E25=""),"",D25*E25)</f>
-        <v/>
-      </c>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="23">
-        <f>IF(OR(F25="",G25="",G25=0),"",F25/G25*1000)</f>
-        <v/>
-      </c>
-      <c r="J25" s="18" t="n"/>
+      <c r="A25" s="21" t="n"/>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="25">
+        <f>IF(OR(E25="",F25="",F25=0),"",E25/F25*1000)</f>
+        <v/>
+      </c>
+      <c r="J25" s="25">
+        <f>IF(OR(E25="",G25="",G25=0),"",E25/G25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="21" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n"/>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="21">
-        <f>IF(OR(D26="",E26=""),"",D26*E26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="23">
-        <f>IF(OR(F26="",G26="",G26=0),"",F26/G26*1000)</f>
-        <v/>
-      </c>
-      <c r="J26" s="18" t="n"/>
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="25">
+        <f>IF(OR(E26="",F26="",F26=0),"",E26/F26*1000)</f>
+        <v/>
+      </c>
+      <c r="J26" s="25">
+        <f>IF(OR(E26="",G26="",G26=0),"",E26/G26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="21" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n"/>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="21">
-        <f>IF(OR(D27="",E27=""),"",D27*E27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="23">
-        <f>IF(OR(F27="",G27="",G27=0),"",F27/G27*1000)</f>
-        <v/>
-      </c>
-      <c r="J27" s="18" t="n"/>
+      <c r="A27" s="21" t="n"/>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="25">
+        <f>IF(OR(E27="",F27="",F27=0),"",E27/F27*1000)</f>
+        <v/>
+      </c>
+      <c r="J27" s="25">
+        <f>IF(OR(E27="",G27="",G27=0),"",E27/G27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="21" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n"/>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="21">
-        <f>IF(OR(D28="",E28=""),"",D28*E28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="23">
-        <f>IF(OR(F28="",G28="",G28=0),"",F28/G28*1000)</f>
-        <v/>
-      </c>
-      <c r="J28" s="18" t="n"/>
+      <c r="A28" s="21" t="n"/>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="25">
+        <f>IF(OR(E28="",F28="",F28=0),"",E28/F28*1000)</f>
+        <v/>
+      </c>
+      <c r="J28" s="25">
+        <f>IF(OR(E28="",G28="",G28=0),"",E28/G28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="21" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n"/>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="21">
-        <f>IF(OR(D29="",E29=""),"",D29*E29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="23">
-        <f>IF(OR(F29="",G29="",G29=0),"",F29/G29*1000)</f>
-        <v/>
-      </c>
-      <c r="J29" s="18" t="n"/>
+      <c r="A29" s="21" t="n"/>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="25">
+        <f>IF(OR(E29="",F29="",F29=0),"",E29/F29*1000)</f>
+        <v/>
+      </c>
+      <c r="J29" s="25">
+        <f>IF(OR(E29="",G29="",G29=0),"",E29/G29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="21" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="25">
+        <f>IF(OR(E30="",F30="",F30=0),"",E30/F30*1000)</f>
+        <v/>
+      </c>
+      <c r="J30" s="25">
+        <f>IF(OR(E30="",G30="",G30=0),"",E30/G30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="25">
+        <f>IF(OR(E31="",F31="",F31=0),"",E31/F31*1000)</f>
+        <v/>
+      </c>
+      <c r="J31" s="25">
+        <f>IF(OR(E31="",G31="",G31=0),"",E31/G31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="25">
+        <f>IF(OR(E32="",F32="",F32=0),"",E32/F32*1000)</f>
+        <v/>
+      </c>
+      <c r="J32" s="25">
+        <f>IF(OR(E32="",G32="",G32=0),"",E32/G32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>8月 月計 / 月合计</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="26">
-        <f>SUM(D18:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="27">
-        <f>SUM(F18:F29)</f>
-        <v/>
-      </c>
-      <c r="G30" s="26">
-        <f>SUM(G18:G29)</f>
-        <v/>
-      </c>
-      <c r="H30" s="26">
-        <f>SUM(H18:H29)</f>
-        <v/>
-      </c>
-      <c r="I30" s="26">
-        <f>IF(G30=0,"",F30/G30*1000)</f>
-        <v/>
-      </c>
-      <c r="J30" s="25" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="28">
+        <f>SUM(D21:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="29">
+        <f>SUM(E21:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>SUM(F21:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="28">
+        <f>SUM(G21:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="28">
+        <f>SUM(H21:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="28">
+        <f>IF(F33=0,"",E33/F33*1000)</f>
+        <v/>
+      </c>
+      <c r="J33" s="28">
+        <f>IF(G33=0,"",E33/G33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="27" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>■ 9月 明細</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>アカウント名
 账号</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>フォロワー層
-层级</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>層級</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>投稿形式
 形式</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>投稿数
 篇数</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>単価(円)
-单价</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>支払金額(円)
-小计</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>稿費(円)
+稿费</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>想定インプレ
-预期曝光</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
+预估曝光</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>想定エンゲージ
-预期互动</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
+预估互动</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>想定保存
+预估收藏</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>CPM(円)</t>
         </is>
       </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>備考
-备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>CPE(円)
+单次互动</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>单眼皮的妮可</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>KOC</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D36" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="20" t="n">
+      <c r="E36" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="F33" s="21">
-        <f>IF(OR(D33="",E33=""),"",D33*E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="22" t="n">
+      <c r="F36" s="24" t="n">
         <v>15000</v>
       </c>
-      <c r="H33" s="22" t="n">
+      <c r="G36" s="24" t="n">
         <v>600</v>
       </c>
-      <c r="I33" s="23">
-        <f>IF(OR(F33="",G33="",G33=0),"",F33/G33*1000)</f>
-        <v/>
-      </c>
-      <c r="J33" s="18" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="H36" s="24" t="n">
+        <v>320</v>
+      </c>
+      <c r="I36" s="25">
+        <f>IF(OR(E36="",F36="",F36=0),"",E36/F36*1000)</f>
+        <v/>
+      </c>
+      <c r="J36" s="25">
+        <f>IF(OR(E36="",G36="",G36=0),"",E36/G36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="21" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>(头部造势·待定)</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>頭部</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>動画(视频)</t>
         </is>
       </c>
-      <c r="D34" s="19" t="n">
+      <c r="D37" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="20" t="n">
+      <c r="E37" s="23" t="n">
         <v>200000</v>
       </c>
-      <c r="F34" s="21">
-        <f>IF(OR(D34="",E34=""),"",D34*E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="22" t="n">
+      <c r="F37" s="24" t="n">
         <v>300000</v>
       </c>
-      <c r="H34" s="22" t="n">
+      <c r="G37" s="24" t="n">
         <v>9000</v>
       </c>
-      <c r="I34" s="23">
-        <f>IF(OR(F34="",G34="",G34=0),"",F34/G34*1000)</f>
-        <v/>
-      </c>
-      <c r="J34" s="18" t="inlineStr">
+      <c r="H37" s="24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I37" s="25">
+        <f>IF(OR(E37="",F37="",F37=0),"",E37/F37*1000)</f>
+        <v/>
+      </c>
+      <c r="J37" s="25">
+        <f>IF(OR(E37="",G37="",G37=0),"",E37/G37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>造势</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>腰部攻略</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>腰部</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D38" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="20" t="n">
+      <c r="E38" s="23" t="n">
         <v>45000</v>
       </c>
-      <c r="F35" s="21">
-        <f>IF(OR(D35="",E35=""),"",D35*E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="22" t="n">
+      <c r="F38" s="24" t="n">
         <v>90000</v>
       </c>
-      <c r="H35" s="22" t="n">
+      <c r="G38" s="24" t="n">
         <v>2700</v>
       </c>
-      <c r="I35" s="23">
-        <f>IF(OR(F35="",G35="",G35=0),"",F35/G35*1000)</f>
-        <v/>
-      </c>
-      <c r="J35" s="18" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="n"/>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="21">
-        <f>IF(OR(D36="",E36=""),"",D36*E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="22" t="n"/>
-      <c r="I36" s="23">
-        <f>IF(OR(F36="",G36="",G36=0),"",F36/G36*1000)</f>
-        <v/>
-      </c>
-      <c r="J36" s="18" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="n"/>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="20" t="n"/>
-      <c r="F37" s="21">
-        <f>IF(OR(D37="",E37=""),"",D37*E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="22" t="n"/>
-      <c r="H37" s="22" t="n"/>
-      <c r="I37" s="23">
-        <f>IF(OR(F37="",G37="",G37=0),"",F37/G37*1000)</f>
-        <v/>
-      </c>
-      <c r="J37" s="18" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="n"/>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="21">
-        <f>IF(OR(D38="",E38=""),"",D38*E38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="23">
-        <f>IF(OR(F38="",G38="",G38=0),"",F38/G38*1000)</f>
-        <v/>
-      </c>
-      <c r="J38" s="18" t="n"/>
+      <c r="H38" s="24" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I38" s="25">
+        <f>IF(OR(E38="",F38="",F38=0),"",E38/F38*1000)</f>
+        <v/>
+      </c>
+      <c r="J38" s="25">
+        <f>IF(OR(E38="",G38="",G38=0),"",E38/G38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>怎么选攻略</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n"/>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="21">
-        <f>IF(OR(D39="",E39=""),"",D39*E39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="22" t="n"/>
-      <c r="I39" s="23">
-        <f>IF(OR(F39="",G39="",G39=0),"",F39/G39*1000)</f>
-        <v/>
-      </c>
-      <c r="J39" s="18" t="n"/>
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="25">
+        <f>IF(OR(E39="",F39="",F39=0),"",E39/F39*1000)</f>
+        <v/>
+      </c>
+      <c r="J39" s="25">
+        <f>IF(OR(E39="",G39="",G39=0),"",E39/G39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="21" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n"/>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="21">
-        <f>IF(OR(D40="",E40=""),"",D40*E40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="22" t="n"/>
-      <c r="H40" s="22" t="n"/>
-      <c r="I40" s="23">
-        <f>IF(OR(F40="",G40="",G40=0),"",F40/G40*1000)</f>
-        <v/>
-      </c>
-      <c r="J40" s="18" t="n"/>
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="24" t="n"/>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="25">
+        <f>IF(OR(E40="",F40="",F40=0),"",E40/F40*1000)</f>
+        <v/>
+      </c>
+      <c r="J40" s="25">
+        <f>IF(OR(E40="",G40="",G40=0),"",E40/G40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="21" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n"/>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="21">
-        <f>IF(OR(D41="",E41=""),"",D41*E41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="22" t="n"/>
-      <c r="I41" s="23">
-        <f>IF(OR(F41="",G41="",G41=0),"",F41/G41*1000)</f>
-        <v/>
-      </c>
-      <c r="J41" s="18" t="n"/>
+      <c r="A41" s="21" t="n"/>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="24" t="n"/>
+      <c r="G41" s="24" t="n"/>
+      <c r="H41" s="24" t="n"/>
+      <c r="I41" s="25">
+        <f>IF(OR(E41="",F41="",F41=0),"",E41/F41*1000)</f>
+        <v/>
+      </c>
+      <c r="J41" s="25">
+        <f>IF(OR(E41="",G41="",G41=0),"",E41/G41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="21" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n"/>
-      <c r="B42" s="19" t="n"/>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="21">
-        <f>IF(OR(D42="",E42=""),"",D42*E42)</f>
-        <v/>
-      </c>
-      <c r="G42" s="22" t="n"/>
-      <c r="H42" s="22" t="n"/>
-      <c r="I42" s="23">
-        <f>IF(OR(F42="",G42="",G42=0),"",F42/G42*1000)</f>
-        <v/>
-      </c>
-      <c r="J42" s="18" t="n"/>
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="23" t="n"/>
+      <c r="F42" s="24" t="n"/>
+      <c r="G42" s="24" t="n"/>
+      <c r="H42" s="24" t="n"/>
+      <c r="I42" s="25">
+        <f>IF(OR(E42="",F42="",F42=0),"",E42/F42*1000)</f>
+        <v/>
+      </c>
+      <c r="J42" s="25">
+        <f>IF(OR(E42="",G42="",G42=0),"",E42/G42)</f>
+        <v/>
+      </c>
+      <c r="K42" s="21" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n"/>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="20" t="n"/>
-      <c r="F43" s="21">
-        <f>IF(OR(D43="",E43=""),"",D43*E43)</f>
-        <v/>
-      </c>
-      <c r="G43" s="22" t="n"/>
-      <c r="H43" s="22" t="n"/>
-      <c r="I43" s="23">
-        <f>IF(OR(F43="",G43="",G43=0),"",F43/G43*1000)</f>
-        <v/>
-      </c>
-      <c r="J43" s="18" t="n"/>
+      <c r="A43" s="21" t="n"/>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="24" t="n"/>
+      <c r="G43" s="24" t="n"/>
+      <c r="H43" s="24" t="n"/>
+      <c r="I43" s="25">
+        <f>IF(OR(E43="",F43="",F43=0),"",E43/F43*1000)</f>
+        <v/>
+      </c>
+      <c r="J43" s="25">
+        <f>IF(OR(E43="",G43="",G43=0),"",E43/G43)</f>
+        <v/>
+      </c>
+      <c r="K43" s="21" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n"/>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="21">
-        <f>IF(OR(D44="",E44=""),"",D44*E44)</f>
-        <v/>
-      </c>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="23">
-        <f>IF(OR(F44="",G44="",G44=0),"",F44/G44*1000)</f>
-        <v/>
-      </c>
-      <c r="J44" s="18" t="n"/>
+      <c r="A44" s="21" t="n"/>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="23" t="n"/>
+      <c r="F44" s="24" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="n"/>
+      <c r="I44" s="25">
+        <f>IF(OR(E44="",F44="",F44=0),"",E44/F44*1000)</f>
+        <v/>
+      </c>
+      <c r="J44" s="25">
+        <f>IF(OR(E44="",G44="",G44=0),"",E44/G44)</f>
+        <v/>
+      </c>
+      <c r="K44" s="21" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="24" t="n"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="25">
+        <f>IF(OR(E45="",F45="",F45=0),"",E45/F45*1000)</f>
+        <v/>
+      </c>
+      <c r="J45" s="25">
+        <f>IF(OR(E45="",G45="",G45=0),"",E45/G45)</f>
+        <v/>
+      </c>
+      <c r="K45" s="21" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="22" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="24" t="n"/>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="24" t="n"/>
+      <c r="I46" s="25">
+        <f>IF(OR(E46="",F46="",F46=0),"",E46/F46*1000)</f>
+        <v/>
+      </c>
+      <c r="J46" s="25">
+        <f>IF(OR(E46="",G46="",G46=0),"",E46/G46)</f>
+        <v/>
+      </c>
+      <c r="K46" s="21" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="23" t="n"/>
+      <c r="F47" s="24" t="n"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+      <c r="I47" s="25">
+        <f>IF(OR(E47="",F47="",F47=0),"",E47/F47*1000)</f>
+        <v/>
+      </c>
+      <c r="J47" s="25">
+        <f>IF(OR(E47="",G47="",G47=0),"",E47/G47)</f>
+        <v/>
+      </c>
+      <c r="K47" s="21" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>9月 月計 / 月合计</t>
         </is>
       </c>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="26">
-        <f>SUM(D33:D44)</f>
-        <v/>
-      </c>
-      <c r="E45" s="25" t="n"/>
-      <c r="F45" s="27">
-        <f>SUM(F33:F44)</f>
-        <v/>
-      </c>
-      <c r="G45" s="26">
-        <f>SUM(G33:G44)</f>
-        <v/>
-      </c>
-      <c r="H45" s="26">
-        <f>SUM(H33:H44)</f>
-        <v/>
-      </c>
-      <c r="I45" s="26">
-        <f>IF(G45=0,"",F45/G45*1000)</f>
-        <v/>
-      </c>
-      <c r="J45" s="25" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="B48" s="27" t="n"/>
+      <c r="C48" s="27" t="n"/>
+      <c r="D48" s="28">
+        <f>SUM(D36:D47)</f>
+        <v/>
+      </c>
+      <c r="E48" s="29">
+        <f>SUM(E36:E47)</f>
+        <v/>
+      </c>
+      <c r="F48" s="28">
+        <f>SUM(F36:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="28">
+        <f>SUM(G36:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="28">
+        <f>SUM(H36:H47)</f>
+        <v/>
+      </c>
+      <c r="I48" s="28">
+        <f>IF(F48=0,"",E48/F48*1000)</f>
+        <v/>
+      </c>
+      <c r="J48" s="28">
+        <f>IF(G48=0,"",E48/G48)</f>
+        <v/>
+      </c>
+      <c r="K48" s="27" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>■ 10月 明細</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>アカウント名
 账号</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>フォロワー層
-层级</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>層級</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>投稿形式
 形式</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>投稿数
 篇数</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>単価(円)
-单价</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>支払金額(円)
-小计</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>稿費(円)
+稿费</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>想定インプレ
-预期曝光</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
+预估曝光</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>想定エンゲージ
-预期互动</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
+预估互动</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>想定保存
+预估收藏</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>CPM(円)</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>備考
-备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>CPE(円)
+单次互动</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>KOC铺量·多人</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B51" s="22" t="inlineStr">
         <is>
           <t>KOC</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D48" s="19" t="n">
+      <c r="D51" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="E48" s="20" t="n">
+      <c r="E51" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="F48" s="21">
-        <f>IF(OR(D48="",E48=""),"",D48*E48)</f>
-        <v/>
-      </c>
-      <c r="G48" s="22" t="n">
+      <c r="F51" s="24" t="n">
         <v>12000</v>
       </c>
-      <c r="H48" s="22" t="n">
+      <c r="G51" s="24" t="n">
         <v>480</v>
       </c>
-      <c r="I48" s="23">
-        <f>IF(OR(F48="",G48="",G48=0),"",F48/G48*1000)</f>
-        <v/>
-      </c>
-      <c r="J48" s="18" t="inlineStr">
+      <c r="H51" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="I51" s="25">
+        <f>IF(OR(E51="",F51="",F51=0),"",E51/F51*1000)</f>
+        <v/>
+      </c>
+      <c r="J51" s="25">
+        <f>IF(OR(E51="",G51="",G51=0),"",E51/G51)</f>
+        <v/>
+      </c>
+      <c r="K51" s="21" t="inlineStr">
         <is>
           <t>双11蓄水</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>腰部攻略</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>腰部</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>画像(图文)</t>
         </is>
       </c>
-      <c r="D49" s="19" t="n">
+      <c r="D52" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="20" t="n">
+      <c r="E52" s="23" t="n">
         <v>45000</v>
       </c>
-      <c r="F49" s="21">
-        <f>IF(OR(D49="",E49=""),"",D49*E49)</f>
-        <v/>
-      </c>
-      <c r="G49" s="22" t="n">
+      <c r="F52" s="24" t="n">
         <v>90000</v>
       </c>
-      <c r="H49" s="22" t="n">
+      <c r="G52" s="24" t="n">
         <v>2700</v>
       </c>
-      <c r="I49" s="23">
-        <f>IF(OR(F49="",G49="",G49=0),"",F49/G49*1000)</f>
-        <v/>
-      </c>
-      <c r="J49" s="18" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="18" t="n"/>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-      <c r="E50" s="20" t="n"/>
-      <c r="F50" s="21">
-        <f>IF(OR(D50="",E50=""),"",D50*E50)</f>
-        <v/>
-      </c>
-      <c r="G50" s="22" t="n"/>
-      <c r="H50" s="22" t="n"/>
-      <c r="I50" s="23">
-        <f>IF(OR(F50="",G50="",G50=0),"",F50/G50*1000)</f>
-        <v/>
-      </c>
-      <c r="J50" s="18" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="n"/>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="21">
-        <f>IF(OR(D51="",E51=""),"",D51*E51)</f>
-        <v/>
-      </c>
-      <c r="G51" s="22" t="n"/>
-      <c r="H51" s="22" t="n"/>
-      <c r="I51" s="23">
-        <f>IF(OR(F51="",G51="",G51=0),"",F51/G51*1000)</f>
-        <v/>
-      </c>
-      <c r="J51" s="18" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="n"/>
-      <c r="B52" s="19" t="n"/>
-      <c r="C52" s="19" t="n"/>
-      <c r="D52" s="19" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="21">
-        <f>IF(OR(D52="",E52=""),"",D52*E52)</f>
-        <v/>
-      </c>
-      <c r="G52" s="22" t="n"/>
-      <c r="H52" s="22" t="n"/>
-      <c r="I52" s="23">
-        <f>IF(OR(F52="",G52="",G52=0),"",F52/G52*1000)</f>
-        <v/>
-      </c>
-      <c r="J52" s="18" t="n"/>
+      <c r="H52" s="24" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I52" s="25">
+        <f>IF(OR(E52="",F52="",F52=0),"",E52/F52*1000)</f>
+        <v/>
+      </c>
+      <c r="J52" s="25">
+        <f>IF(OR(E52="",G52="",G52=0),"",E52/G52)</f>
+        <v/>
+      </c>
+      <c r="K52" s="21" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n"/>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="21">
-        <f>IF(OR(D53="",E53=""),"",D53*E53)</f>
-        <v/>
-      </c>
-      <c r="G53" s="22" t="n"/>
-      <c r="H53" s="22" t="n"/>
-      <c r="I53" s="23">
-        <f>IF(OR(F53="",G53="",G53=0),"",F53/G53*1000)</f>
-        <v/>
-      </c>
-      <c r="J53" s="18" t="n"/>
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="22" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="23" t="n"/>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="25">
+        <f>IF(OR(E53="",F53="",F53=0),"",E53/F53*1000)</f>
+        <v/>
+      </c>
+      <c r="J53" s="25">
+        <f>IF(OR(E53="",G53="",G53=0),"",E53/G53)</f>
+        <v/>
+      </c>
+      <c r="K53" s="21" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n"/>
-      <c r="B54" s="19" t="n"/>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="19" t="n"/>
-      <c r="E54" s="20" t="n"/>
-      <c r="F54" s="21">
-        <f>IF(OR(D54="",E54=""),"",D54*E54)</f>
-        <v/>
-      </c>
-      <c r="G54" s="22" t="n"/>
-      <c r="H54" s="22" t="n"/>
-      <c r="I54" s="23">
-        <f>IF(OR(F54="",G54="",G54=0),"",F54/G54*1000)</f>
-        <v/>
-      </c>
-      <c r="J54" s="18" t="n"/>
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="23" t="n"/>
+      <c r="F54" s="24" t="n"/>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="24" t="n"/>
+      <c r="I54" s="25">
+        <f>IF(OR(E54="",F54="",F54=0),"",E54/F54*1000)</f>
+        <v/>
+      </c>
+      <c r="J54" s="25">
+        <f>IF(OR(E54="",G54="",G54=0),"",E54/G54)</f>
+        <v/>
+      </c>
+      <c r="K54" s="21" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n"/>
-      <c r="B55" s="19" t="n"/>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="21">
-        <f>IF(OR(D55="",E55=""),"",D55*E55)</f>
-        <v/>
-      </c>
-      <c r="G55" s="22" t="n"/>
-      <c r="H55" s="22" t="n"/>
-      <c r="I55" s="23">
-        <f>IF(OR(F55="",G55="",G55=0),"",F55/G55*1000)</f>
-        <v/>
-      </c>
-      <c r="J55" s="18" t="n"/>
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="22" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="24" t="n"/>
+      <c r="G55" s="24" t="n"/>
+      <c r="H55" s="24" t="n"/>
+      <c r="I55" s="25">
+        <f>IF(OR(E55="",F55="",F55=0),"",E55/F55*1000)</f>
+        <v/>
+      </c>
+      <c r="J55" s="25">
+        <f>IF(OR(E55="",G55="",G55=0),"",E55/G55)</f>
+        <v/>
+      </c>
+      <c r="K55" s="21" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n"/>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
-      <c r="E56" s="20" t="n"/>
-      <c r="F56" s="21">
-        <f>IF(OR(D56="",E56=""),"",D56*E56)</f>
-        <v/>
-      </c>
-      <c r="G56" s="22" t="n"/>
-      <c r="H56" s="22" t="n"/>
-      <c r="I56" s="23">
-        <f>IF(OR(F56="",G56="",G56=0),"",F56/G56*1000)</f>
-        <v/>
-      </c>
-      <c r="J56" s="18" t="n"/>
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="22" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="23" t="n"/>
+      <c r="F56" s="24" t="n"/>
+      <c r="G56" s="24" t="n"/>
+      <c r="H56" s="24" t="n"/>
+      <c r="I56" s="25">
+        <f>IF(OR(E56="",F56="",F56=0),"",E56/F56*1000)</f>
+        <v/>
+      </c>
+      <c r="J56" s="25">
+        <f>IF(OR(E56="",G56="",G56=0),"",E56/G56)</f>
+        <v/>
+      </c>
+      <c r="K56" s="21" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n"/>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="21">
-        <f>IF(OR(D57="",E57=""),"",D57*E57)</f>
-        <v/>
-      </c>
-      <c r="G57" s="22" t="n"/>
-      <c r="H57" s="22" t="n"/>
-      <c r="I57" s="23">
-        <f>IF(OR(F57="",G57="",G57=0),"",F57/G57*1000)</f>
-        <v/>
-      </c>
-      <c r="J57" s="18" t="n"/>
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="22" t="n"/>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="23" t="n"/>
+      <c r="F57" s="24" t="n"/>
+      <c r="G57" s="24" t="n"/>
+      <c r="H57" s="24" t="n"/>
+      <c r="I57" s="25">
+        <f>IF(OR(E57="",F57="",F57=0),"",E57/F57*1000)</f>
+        <v/>
+      </c>
+      <c r="J57" s="25">
+        <f>IF(OR(E57="",G57="",G57=0),"",E57/G57)</f>
+        <v/>
+      </c>
+      <c r="K57" s="21" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n"/>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="20" t="n"/>
-      <c r="F58" s="21">
-        <f>IF(OR(D58="",E58=""),"",D58*E58)</f>
-        <v/>
-      </c>
-      <c r="G58" s="22" t="n"/>
-      <c r="H58" s="22" t="n"/>
-      <c r="I58" s="23">
-        <f>IF(OR(F58="",G58="",G58=0),"",F58/G58*1000)</f>
-        <v/>
-      </c>
-      <c r="J58" s="18" t="n"/>
+      <c r="A58" s="21" t="n"/>
+      <c r="B58" s="22" t="n"/>
+      <c r="C58" s="22" t="n"/>
+      <c r="D58" s="22" t="n"/>
+      <c r="E58" s="23" t="n"/>
+      <c r="F58" s="24" t="n"/>
+      <c r="G58" s="24" t="n"/>
+      <c r="H58" s="24" t="n"/>
+      <c r="I58" s="25">
+        <f>IF(OR(E58="",F58="",F58=0),"",E58/F58*1000)</f>
+        <v/>
+      </c>
+      <c r="J58" s="25">
+        <f>IF(OR(E58="",G58="",G58=0),"",E58/G58)</f>
+        <v/>
+      </c>
+      <c r="K58" s="21" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n"/>
-      <c r="B59" s="19" t="n"/>
-      <c r="C59" s="19" t="n"/>
-      <c r="D59" s="19" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="21">
-        <f>IF(OR(D59="",E59=""),"",D59*E59)</f>
-        <v/>
-      </c>
-      <c r="G59" s="22" t="n"/>
-      <c r="H59" s="22" t="n"/>
-      <c r="I59" s="23">
-        <f>IF(OR(F59="",G59="",G59=0),"",F59/G59*1000)</f>
-        <v/>
-      </c>
-      <c r="J59" s="18" t="n"/>
+      <c r="A59" s="21" t="n"/>
+      <c r="B59" s="22" t="n"/>
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="22" t="n"/>
+      <c r="E59" s="23" t="n"/>
+      <c r="F59" s="24" t="n"/>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="24" t="n"/>
+      <c r="I59" s="25">
+        <f>IF(OR(E59="",F59="",F59=0),"",E59/F59*1000)</f>
+        <v/>
+      </c>
+      <c r="J59" s="25">
+        <f>IF(OR(E59="",G59="",G59=0),"",E59/G59)</f>
+        <v/>
+      </c>
+      <c r="K59" s="21" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="22" t="n"/>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="23" t="n"/>
+      <c r="F60" s="24" t="n"/>
+      <c r="G60" s="24" t="n"/>
+      <c r="H60" s="24" t="n"/>
+      <c r="I60" s="25">
+        <f>IF(OR(E60="",F60="",F60=0),"",E60/F60*1000)</f>
+        <v/>
+      </c>
+      <c r="J60" s="25">
+        <f>IF(OR(E60="",G60="",G60=0),"",E60/G60)</f>
+        <v/>
+      </c>
+      <c r="K60" s="21" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="n"/>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="23" t="n"/>
+      <c r="F61" s="24" t="n"/>
+      <c r="G61" s="24" t="n"/>
+      <c r="H61" s="24" t="n"/>
+      <c r="I61" s="25">
+        <f>IF(OR(E61="",F61="",F61=0),"",E61/F61*1000)</f>
+        <v/>
+      </c>
+      <c r="J61" s="25">
+        <f>IF(OR(E61="",G61="",G61=0),"",E61/G61)</f>
+        <v/>
+      </c>
+      <c r="K61" s="21" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="n"/>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="23" t="n"/>
+      <c r="F62" s="24" t="n"/>
+      <c r="G62" s="24" t="n"/>
+      <c r="H62" s="24" t="n"/>
+      <c r="I62" s="25">
+        <f>IF(OR(E62="",F62="",F62=0),"",E62/F62*1000)</f>
+        <v/>
+      </c>
+      <c r="J62" s="25">
+        <f>IF(OR(E62="",G62="",G62=0),"",E62/G62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="21" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>10月 月計 / 月合计</t>
         </is>
       </c>
-      <c r="B60" s="25" t="n"/>
-      <c r="C60" s="25" t="n"/>
-      <c r="D60" s="26">
-        <f>SUM(D48:D59)</f>
-        <v/>
-      </c>
-      <c r="E60" s="25" t="n"/>
-      <c r="F60" s="27">
-        <f>SUM(F48:F59)</f>
-        <v/>
-      </c>
-      <c r="G60" s="26">
-        <f>SUM(G48:G59)</f>
-        <v/>
-      </c>
-      <c r="H60" s="26">
-        <f>SUM(H48:H59)</f>
-        <v/>
-      </c>
-      <c r="I60" s="26">
-        <f>IF(G60=0,"",F60/G60*1000)</f>
-        <v/>
-      </c>
-      <c r="J60" s="25" t="n"/>
+      <c r="B63" s="27" t="n"/>
+      <c r="C63" s="27" t="n"/>
+      <c r="D63" s="28">
+        <f>SUM(D51:D62)</f>
+        <v/>
+      </c>
+      <c r="E63" s="29">
+        <f>SUM(E51:E62)</f>
+        <v/>
+      </c>
+      <c r="F63" s="28">
+        <f>SUM(F51:F62)</f>
+        <v/>
+      </c>
+      <c r="G63" s="28">
+        <f>SUM(G51:G62)</f>
+        <v/>
+      </c>
+      <c r="H63" s="28">
+        <f>SUM(H51:H62)</f>
+        <v/>
+      </c>
+      <c r="I63" s="28">
+        <f>IF(F63=0,"",E63/F63*1000)</f>
+        <v/>
+      </c>
+      <c r="J63" s="28">
+        <f>IF(G63=0,"",E63/G63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="27" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>⑤ 给品牌方看的数据说明 ／ ブランド様への報告指標</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>1. 投入：篇数 / 稿费(预算) / 达人层级分布。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>2. 内容表现：曝光 / 互动 / 互动率 / 收藏(收藏率) / 爆文数。※收藏率=种草意向强信号；只看曝光会被『高曝低互动』骗到。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>3. 种草衔接(最关键·投后回填)：小红书品牌/产品搜索指数变化 · A3深度种草人群增量(专业号后台) · 天猫搜索入店/加购/成交(关联来源)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>4. 效率：CPM(千次曝光成本) · CPE(单次互动成本)。※笔记不用ROAS/GMV当主口径(无小红书店、归因模糊)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>5. 预估 vs 实际：投前给目标，投后回填实际算达成率——最能让品牌方放心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>本表=投放前『预算+预估效果』；投后建议同结构再建一张『实际效果』做对比。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A16:J16"/>
+  <mergeCells count="15">
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="B18:B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B21:B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"頭部,腰部,尾部,KOC"</formula1>
     </dataValidation>
-    <dataValidation sqref="C18:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C21:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"画像(图文),動画(视频)"</formula1>
     </dataValidation>
-    <dataValidation sqref="B33:B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B36:B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"頭部,腰部,尾部,KOC"</formula1>
     </dataValidation>
-    <dataValidation sqref="C33:C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C36:C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"画像(图文),動画(视频)"</formula1>
     </dataValidation>
-    <dataValidation sqref="B48:B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B51:B62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"頭部,腰部,尾部,KOC"</formula1>
     </dataValidation>
-    <dataValidation sqref="C48:C59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C51:C62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"画像(图文),動画(视频)"</formula1>
     </dataValidation>
   </dataValidations>
